--- a/artfynd/A 9245-2022 artfynd.xlsx
+++ b/artfynd/A 9245-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9245-2022 artfynd.xlsx
+++ b/artfynd/A 9245-2022 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>117765030</v>
       </c>
       <c r="B11" t="n">
-        <v>57557</v>
+        <v>57558</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 9245-2022 artfynd.xlsx
+++ b/artfynd/A 9245-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,6 +1829,120 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122835210</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57749</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lundsångare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phylloscopus trochiloides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Sundevall, 1837)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Raningsbäcken, Klabböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>752456</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7087620</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marcus Östman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Alriksson, Random Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9245-2022 artfynd.xlsx
+++ b/artfynd/A 9245-2022 artfynd.xlsx
@@ -1834,7 +1834,7 @@
         <v>122835210</v>
       </c>
       <c r="B12" t="n">
-        <v>57749</v>
+        <v>57752</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
